--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-09-29 14:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:04</t>
+    <t xml:space="preserve">2026-09-29 18:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,10 +493,10 @@
         <v>3.69</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>72.13</v>
+        <v>72.12</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>68.43</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="3">
@@ -521,10 +521,10 @@
         <v>-2.51</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>68.97</v>
+        <v>68.98</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>71.49</v>
+        <v>71.48</v>
       </c>
     </row>
     <row r="5">

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_aysen_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_aysen_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:37</t>
+    <t xml:space="preserve">2026-10-05 04:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -493,7 +493,7 @@
         <v>3.69</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>72.12</v>
+        <v>72.13</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>68.44</v>
@@ -524,7 +524,7 @@
         <v>68.98</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>71.48</v>
+        <v>71.49</v>
       </c>
     </row>
     <row r="5">
